--- a/output/final_metrics.xlsx
+++ b/output/final_metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Automobile Insurance Fraud Detection\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA1D5CE-6ED3-4CF4-81BC-2C4FEB7CC327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A4F426C-A2F4-4EB9-88F1-C1A17B2CF7CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,62 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>Best Model: Gradient Boosting Classifier</t>
-  </si>
-  <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Score</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Selected Threshold:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 0.40</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Note: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Results may vary based on different thresholds</t>
-    </r>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>Accuracy</t>
   </si>
@@ -94,7 +39,22 @@
     <t>F1-score</t>
   </si>
   <si>
-    <t>ROC-AUC</t>
+    <t>Selected Models:</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>Threshold</t>
+  </si>
+  <si>
+    <t>ROC-AUC Score</t>
+  </si>
+  <si>
+    <t>Random Forest</t>
+  </si>
+  <si>
+    <t>Decision Tree</t>
   </si>
 </sst>
 </file>
@@ -127,18 +87,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -146,18 +106,38 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -438,80 +418,101 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="10.1796875" customWidth="1"/>
+    <col min="1" max="1" width="15.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="4"/>
+      <c r="D5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>3</v>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.86</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.19</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.42</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.26</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0.81</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>0.88239999999999996</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>0.18940000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>0.30330000000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>0.23319999999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B11">
-        <v>0.80559999999999998</v>
+      <c r="B7" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0.52</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0.23</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0.79</v>
       </c>
     </row>
   </sheetData>
